--- a/Puchar_Lata_2026_Browar.xlsx
+++ b/Puchar_Lata_2026_Browar.xlsx
@@ -609,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S93"/>
+  <dimension ref="A1:S105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2167,921 +2167,573 @@
       </c>
     </row>
     <row r="51"/>
-    <row r="52"/>
+    <row r="52">
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>Runda XII • Piątek, 07.08.2026</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
-      <c r="B53" s="1" t="inlineStr">
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>Bieg</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="J53" s="20" t="inlineStr">
+        <is>
+          <t>DAH</t>
+        </is>
+      </c>
+      <c r="K53" s="20" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="M53" s="20" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="N53" s="20" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 1</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F54" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H54" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="I54" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L54" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M54" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N54" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 2</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="D55" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I55" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J55" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L55" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M55" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 3</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E56" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H56" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="I56" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K56" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L56" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 4</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="E57" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F57" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G57" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J57" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K57" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L57" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M57" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N57" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="21" t="inlineStr">
+        <is>
+          <t>Bieg 5</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="E58" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="G58" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M58" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N58" s="22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>Suma punktów</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D59" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G59" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="H59" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="I59" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="J59" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="K59" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="L59" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="M59" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N59" s="17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="23" t="inlineStr">
+        <is>
+          <t>Średnia na bieg</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D60" s="24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E60" s="24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F60" s="24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G60" s="24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H60" s="24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I60" s="24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J60" s="24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K60" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L60" s="24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M60" s="24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N60" s="24" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="25" t="inlineStr">
+        <is>
+          <t>Miejsce</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I61" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J61" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="K61" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="L61" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="M61" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="N61" s="26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="23" t="inlineStr">
+        <is>
+          <t>Punkty Turniejowe</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G62" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H62" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J62" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K62" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L62" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M62" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N62" s="17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65">
+      <c r="B65" s="1" t="inlineStr">
         <is>
           <t>KLASYFIKACJA GENERALNA PUCHARU (12 RUND)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="3" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Poz.</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Zawodnik</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="M66" s="3" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="N54" s="3" t="inlineStr">
+      <c r="N66" s="3" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
+      <c r="O66" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="P54" s="3" t="inlineStr">
+      <c r="P66" s="3" t="inlineStr">
         <is>
           <t>SUMA</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="27" t="inlineStr">
-        <is>
-          <t>RDX</t>
-        </is>
-      </c>
-      <c r="D55" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="E55" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="F55" s="28" t="n">
-        <v>20</v>
-      </c>
-      <c r="G55" s="28" t="n">
-        <v>20</v>
-      </c>
-      <c r="H55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O55" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P55" s="17" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" s="29" t="inlineStr">
-        <is>
-          <t>SIW</t>
-        </is>
-      </c>
-      <c r="D56" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="E56" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="F56" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="G56" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="H56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O56" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P56" s="17" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" s="27" t="inlineStr">
-        <is>
-          <t>BĄB</t>
-        </is>
-      </c>
-      <c r="D57" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="E57" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="F57" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="G57" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="H57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O57" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P57" s="17" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C58" s="29" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="D58" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="E58" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="F58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="H58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O58" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P58" s="17" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C59" s="27" t="inlineStr">
-        <is>
-          <t>KRO</t>
-        </is>
-      </c>
-      <c r="D59" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="F59" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="G59" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="H59" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I59" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M59" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N59" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O59" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P59" s="17" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="C60" s="29" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="D60" s="30" t="n">
-        <v>16</v>
-      </c>
-      <c r="E60" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="F60" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="H60" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I60" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N60" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O60" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P60" s="17" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="C61" s="27" t="inlineStr">
-        <is>
-          <t>PYR</t>
-        </is>
-      </c>
-      <c r="D61" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="E61" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="F61" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="G61" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="H61" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M61" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O61" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P61" s="17" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="C62" s="29" t="inlineStr">
-        <is>
-          <t>PAW</t>
-        </is>
-      </c>
-      <c r="D62" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="E62" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="F62" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="H62" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O62" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P62" s="17" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="C63" s="27" t="inlineStr">
-        <is>
-          <t>SZP</t>
-        </is>
-      </c>
-      <c r="D63" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E63" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="G63" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M63" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O63" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P63" s="17" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="C64" s="29" t="inlineStr">
-        <is>
-          <t>DAR</t>
-        </is>
-      </c>
-      <c r="D64" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="F64" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="G64" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="H64" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O64" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P64" s="17" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="C65" s="27" t="inlineStr">
-        <is>
-          <t>KAL</t>
-        </is>
-      </c>
-      <c r="D65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="G65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O65" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P65" s="17" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="C66" s="29" t="inlineStr">
-        <is>
-          <t>TAS</t>
-        </is>
-      </c>
-      <c r="D66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="H66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O66" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P66" s="17" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="27" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="D67" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="E67" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="E67" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="F67" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="G67" s="28" t="n">
+        <v>20</v>
       </c>
       <c r="H67" s="28" t="inlineStr">
         <is>
@@ -3118,41 +2770,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O67" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O67" s="28" t="n">
+        <v>10</v>
       </c>
       <c r="P67" s="17" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="C68" s="29" t="inlineStr">
-        <is>
-          <t>CYG</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="E68" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="F68" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="G68" s="30" t="n">
+        <v>18</v>
       </c>
       <c r="H68" s="30" t="inlineStr">
         <is>
@@ -3189,43 +2833,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O68" s="30" t="n">
+        <v>16</v>
       </c>
       <c r="P68" s="17" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="D69" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D69" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="E69" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="F69" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="G69" s="28" t="n">
+        <v>16</v>
       </c>
       <c r="H69" s="28" t="inlineStr">
         <is>
@@ -3262,101 +2896,965 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O69" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O69" s="28" t="n">
+        <v>7</v>
       </c>
       <c r="P69" s="17" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E70" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O70" s="30" t="n">
+        <v>18</v>
+      </c>
+      <c r="P70" s="17" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" s="27" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D71" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="C70" s="29" t="inlineStr">
+      <c r="E71" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F71" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="H71" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M71" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O71" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="P71" s="17" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C72" s="29" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="D72" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" s="30" t="n">
+        <v>18</v>
+      </c>
+      <c r="F72" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G72" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H72" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M72" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O72" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="P72" s="17" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C73" s="27" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="D73" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G73" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H73" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M73" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O73" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="P73" s="17" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E74" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H74" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M74" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O74" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="P74" s="17" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C75" s="27" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D75" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G75" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H75" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M75" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O75" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="P75" s="17" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P76" s="17" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C77" s="27" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="D77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="G77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P77" s="17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="D78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O78" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P78" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="C79" s="27" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="P79" s="17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="C80" s="29" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D80" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O80" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P80" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C81" s="27" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E81" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P81" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>DAH</t>
+        </is>
+      </c>
+      <c r="D82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O82" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="P82" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="C83" s="27" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P70" s="17" t="n">
+      <c r="D83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P83" s="17" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
     <row r="84"/>
     <row r="85"/>
     <row r="86"/>
@@ -3367,6 +3865,18 @@
     <row r="91"/>
     <row r="92"/>
     <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/Puchar_Lata_2026_Browar.xlsx
+++ b/Puchar_Lata_2026_Browar.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S117"/>
+  <dimension ref="A1:S139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3162,892 +3162,646 @@
       </c>
     </row>
     <row r="75"/>
-    <row r="76"/>
+    <row r="76">
+      <c r="B76" s="32" t="inlineStr">
+        <is>
+          <t>Runda VII • Piątek, 21.08.2026</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="B77" s="1" t="inlineStr">
+      <c r="B77" s="33" t="inlineStr">
+        <is>
+          <t>Bieg</t>
+        </is>
+      </c>
+      <c r="C77" s="33" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D77" s="33" t="inlineStr">
+        <is>
+          <t>ROM</t>
+        </is>
+      </c>
+      <c r="E77" s="33" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="F77" s="33" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="G77" s="33" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="I77" s="33" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="K77" s="33" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="L77" s="33" t="inlineStr">
+        <is>
+          <t>BĄC</t>
+        </is>
+      </c>
+      <c r="M77" s="33" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="N77" s="33" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="O77" s="33" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="P77" s="33" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 1</t>
+        </is>
+      </c>
+      <c r="C78" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E78" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="F78" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H78" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I78" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="J78" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K78" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="L78" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="M78" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="N78" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" s="35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 2</t>
+        </is>
+      </c>
+      <c r="C79" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="D79" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="E79" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="F79" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G79" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I79" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K79" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="L79" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="M79" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="O79" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 3</t>
+        </is>
+      </c>
+      <c r="C80" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="D80" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="E80" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F80" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="G80" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="H80" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J80" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K80" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="M80" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P80" s="35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 4</t>
+        </is>
+      </c>
+      <c r="C81" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D81" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="G81" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="I81" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K81" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="L81" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="M81" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="N81" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O81" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P81" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 5</t>
+        </is>
+      </c>
+      <c r="C82" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D82" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="G82" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="H82" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="I82" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K82" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="O82" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="P82" s="35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="36" t="inlineStr">
+        <is>
+          <t>Suma punktów</t>
+        </is>
+      </c>
+      <c r="C83" s="29" t="n">
+        <v>51</v>
+      </c>
+      <c r="D83" s="29" t="n">
+        <v>41</v>
+      </c>
+      <c r="E83" s="29" t="n">
+        <v>40</v>
+      </c>
+      <c r="F83" s="29" t="n">
+        <v>38</v>
+      </c>
+      <c r="G83" s="29" t="n">
+        <v>37</v>
+      </c>
+      <c r="H83" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="I83" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="J83" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="K83" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="L83" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="M83" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="N83" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="O83" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="P83" s="29" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="36" t="inlineStr">
+        <is>
+          <t>Średnia na bieg</t>
+        </is>
+      </c>
+      <c r="C84" s="31" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D84" s="31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E84" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F84" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G84" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H84" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I84" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J84" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K84" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L84" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="M84" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N84" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="O84" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P84" s="31" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="37" t="inlineStr">
+        <is>
+          <t>Miejsce</t>
+        </is>
+      </c>
+      <c r="C85" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G85" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I85" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J85" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="K85" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L85" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="M85" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N85" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="O85" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="P85" s="38" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="36" t="inlineStr">
+        <is>
+          <t>Punkty Turniejowe</t>
+        </is>
+      </c>
+      <c r="C86" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D86" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E86" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="F86" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G86" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H86" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I86" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J86" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L86" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M86" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N86" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O86" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P86" s="29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89">
+      <c r="B89" s="1" t="inlineStr">
         <is>
           <t>KLASYFIKACJA GENERALNA PUCHARU (12 RUND)</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="3" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Poz.</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Zawodnik</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="K78" s="3" t="inlineStr">
+      <c r="K90" s="3" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="L78" s="3" t="inlineStr">
+      <c r="L90" s="3" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="M78" s="3" t="inlineStr">
+      <c r="M90" s="3" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr">
+      <c r="N90" s="3" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="O78" s="3" t="inlineStr">
+      <c r="O90" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="P78" s="3" t="inlineStr">
+      <c r="P90" s="3" t="inlineStr">
         <is>
           <t>SUMA</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" s="39" t="inlineStr">
-        <is>
-          <t>RDX</t>
-        </is>
-      </c>
-      <c r="D79" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="E79" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="F79" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="G79" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="H79" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="I79" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="J79" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M79" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N79" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O79" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P79" s="29" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>SIW</t>
-        </is>
-      </c>
-      <c r="D80" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="E80" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="F80" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="G80" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="H80" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I80" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="J80" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="29" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="C81" s="39" t="inlineStr">
-        <is>
-          <t>BĄB</t>
-        </is>
-      </c>
-      <c r="D81" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="E81" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="F81" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="G81" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="H81" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="I81" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="J81" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M81" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N81" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O81" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P81" s="29" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="D82" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="E82" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="F82" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H82" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="I82" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="J82" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M82" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O82" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P82" s="29" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C83" s="39" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="D83" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="E83" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="F83" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="H83" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="I83" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="J83" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P83" s="29" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>KRO</t>
-        </is>
-      </c>
-      <c r="D84" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="F84" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="G84" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="H84" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="I84" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="J84" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M84" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N84" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O84" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P84" s="29" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="C85" s="39" t="inlineStr">
-        <is>
-          <t>PYR</t>
-        </is>
-      </c>
-      <c r="D85" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="E85" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F85" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="G85" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="H85" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="I85" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="J85" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P85" s="29" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>PAW</t>
-        </is>
-      </c>
-      <c r="D86" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E86" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="F86" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G86" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="H86" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="I86" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="J86" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M86" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N86" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O86" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P86" s="29" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="C87" s="39" t="inlineStr">
-        <is>
-          <t>SZP</t>
-        </is>
-      </c>
-      <c r="D87" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E87" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="F87" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="G87" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="J87" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M87" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N87" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O87" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P87" s="29" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="41" t="n">
-        <v>10</v>
-      </c>
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>DAR</t>
-        </is>
-      </c>
-      <c r="D88" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F88" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="G88" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="H88" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="I88" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="J88" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M88" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N88" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O88" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P88" s="29" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="39" t="n">
-        <v>11</v>
-      </c>
-      <c r="C89" s="39" t="inlineStr">
-        <is>
-          <t>KAL</t>
-        </is>
-      </c>
-      <c r="D89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="G89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="I89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O89" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P89" s="29" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="41" t="n">
-        <v>12</v>
-      </c>
-      <c r="C90" s="41" t="inlineStr">
-        <is>
-          <t>TAS</t>
-        </is>
-      </c>
-      <c r="D90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="H90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="J90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O90" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P90" s="29" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="39" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C91" s="39" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="D91" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="E91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="E91" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="F91" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="G91" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="H91" s="40" t="n">
+        <v>10</v>
       </c>
       <c r="I91" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="J91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="J91" s="40" t="n">
+        <v>16</v>
       </c>
       <c r="K91" s="40" t="inlineStr">
         <is>
@@ -4075,50 +3829,38 @@
         </is>
       </c>
       <c r="P91" s="29" t="n">
-        <v>16</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="41" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="D92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D92" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="E92" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="F92" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="G92" s="42" t="n">
+        <v>16</v>
       </c>
       <c r="H92" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="I92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="I92" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="J92" s="42" t="n">
+        <v>10</v>
       </c>
       <c r="K92" s="42" t="inlineStr">
         <is>
@@ -4146,50 +3888,38 @@
         </is>
       </c>
       <c r="P92" s="29" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C93" s="39" t="inlineStr">
         <is>
-          <t>CYG</t>
-        </is>
-      </c>
-      <c r="D93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="D93" s="40" t="n">
+        <v>14</v>
       </c>
       <c r="E93" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="F93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="F93" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="G93" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="H93" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="I93" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="J93" s="40" t="n">
+        <v>14</v>
       </c>
       <c r="K93" s="40" t="inlineStr">
         <is>
@@ -4217,50 +3947,40 @@
         </is>
       </c>
       <c r="P93" s="29" t="n">
-        <v>8</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C94" s="41" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D94" s="42" t="n">
         <v>16</v>
       </c>
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>DAH</t>
-        </is>
-      </c>
-      <c r="D94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="42" t="n">
+        <v>9</v>
       </c>
       <c r="F94" s="42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G94" s="42" t="n">
+        <v>9</v>
       </c>
       <c r="H94" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="I94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="I94" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="J94" s="42" t="n">
+        <v>20</v>
       </c>
       <c r="K94" s="42" t="inlineStr">
         <is>
@@ -4288,97 +4008,1079 @@
         </is>
       </c>
       <c r="P94" s="29" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C95" s="39" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="D95" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="E95" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="F95" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="H95" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="I95" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="J95" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P95" s="29" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C96" s="41" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="D96" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E96" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="F96" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G96" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="H96" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="I96" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J96" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M96" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O96" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P96" s="29" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="C97" s="39" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="D97" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E97" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F97" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G97" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="H97" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="I97" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="J97" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="K97" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P97" s="29" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C98" s="41" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="D98" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="G98" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="J98" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K98" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M98" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O98" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P98" s="29" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C99" s="39" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="D99" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E99" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F99" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="H99" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I99" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="J99" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P99" s="29" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C100" s="41" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D100" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E100" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F100" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="G100" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="H100" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I100" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="J100" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K100" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M100" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O100" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P100" s="29" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="C101" s="39" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="D101" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E101" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="G101" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I101" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P101" s="29" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="C102" s="41" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="D102" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E102" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="H102" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J102" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K102" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M102" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O102" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P102" s="29" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C103" s="39" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="I103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="K103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P103" s="29" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="C104" s="41" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D104" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E104" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J104" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K104" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M104" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O104" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P104" s="29" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C105" s="39" t="inlineStr">
+        <is>
+          <t>ROM</t>
+        </is>
+      </c>
+      <c r="D105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="K105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P105" s="29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="41" t="n">
+        <v>16</v>
+      </c>
+      <c r="C106" s="41" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E106" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="F106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O106" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P106" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="C95" s="39" t="inlineStr">
+      <c r="C107" s="39" t="inlineStr">
+        <is>
+          <t>DAH</t>
+        </is>
+      </c>
+      <c r="D107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="I107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O107" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P107" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="C108" s="41" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="D108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="K108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P108" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="39" t="n">
+        <v>19</v>
+      </c>
+      <c r="C109" s="39" t="inlineStr">
+        <is>
+          <t>BĄC</t>
+        </is>
+      </c>
+      <c r="D109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="K109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O109" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P109" s="29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C110" s="41" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="D95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P95" s="29" t="n">
+      <c r="D110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P110" s="29" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
     <row r="111"/>
     <row r="112"/>
     <row r="113"/>
@@ -4386,6 +5088,28 @@
     <row r="115"/>
     <row r="116"/>
     <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>

--- a/Puchar_Lata_2026_Browar.xlsx
+++ b/Puchar_Lata_2026_Browar.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S139"/>
+  <dimension ref="A1:S151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3688,879 +3688,649 @@
       </c>
     </row>
     <row r="87"/>
-    <row r="88"/>
+    <row r="88">
+      <c r="B88" s="32" t="inlineStr">
+        <is>
+          <t>Runda VIII • Piątek, 28.08.2026</t>
+        </is>
+      </c>
+    </row>
     <row r="89">
-      <c r="B89" s="1" t="inlineStr">
+      <c r="B89" s="33" t="inlineStr">
+        <is>
+          <t>Bieg</t>
+        </is>
+      </c>
+      <c r="C89" s="33" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D89" s="33" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="E89" s="33" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="F89" s="33" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="G89" s="33" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="H89" s="33" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="I89" s="33" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="J89" s="33" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="K89" s="33" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="L89" s="33" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="M89" s="33" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="N89" s="33" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="O89" s="33" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="P89" s="33" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 1</t>
+        </is>
+      </c>
+      <c r="C90" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D90" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="E90" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F90" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="G90" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="I90" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="J90" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="L90" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="M90" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N90" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P90" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 2</t>
+        </is>
+      </c>
+      <c r="C91" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D91" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="F91" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="G91" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="I91" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J91" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="M91" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="N91" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="O91" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" s="35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 3</t>
+        </is>
+      </c>
+      <c r="C92" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D92" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="F92" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G92" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H92" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I92" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="J92" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K92" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L92" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="M92" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N92" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P92" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 4</t>
+        </is>
+      </c>
+      <c r="C93" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D93" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="E93" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G93" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="H93" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="I93" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J93" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="K93" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="L93" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="N93" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O93" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" s="35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 5</t>
+        </is>
+      </c>
+      <c r="C94" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D94" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="E94" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F94" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="G94" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="I94" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K94" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L94" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M94" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N94" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="O94" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P94" s="35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="36" t="inlineStr">
+        <is>
+          <t>Suma punktów</t>
+        </is>
+      </c>
+      <c r="C95" s="29" t="n">
+        <v>56</v>
+      </c>
+      <c r="D95" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="E95" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="F95" s="29" t="n">
+        <v>37</v>
+      </c>
+      <c r="G95" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="H95" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="I95" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="J95" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="K95" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="L95" s="29" t="n">
+        <v>28</v>
+      </c>
+      <c r="M95" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="N95" s="29" t="n">
+        <v>21</v>
+      </c>
+      <c r="O95" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="P95" s="29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="36" t="inlineStr">
+        <is>
+          <t>Średnia na bieg</t>
+        </is>
+      </c>
+      <c r="C96" s="31" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D96" s="31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E96" s="31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F96" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G96" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H96" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I96" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J96" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K96" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="L96" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M96" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N96" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O96" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P96" s="31" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="37" t="inlineStr">
+        <is>
+          <t>Miejsce</t>
+        </is>
+      </c>
+      <c r="C97" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E97" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G97" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H97" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I97" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J97" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="K97" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L97" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="M97" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N97" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="O97" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="P97" s="38" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="36" t="inlineStr">
+        <is>
+          <t>Punkty Turniejowe</t>
+        </is>
+      </c>
+      <c r="C98" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D98" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E98" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="F98" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G98" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H98" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I98" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J98" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K98" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L98" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M98" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N98" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O98" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P98" s="29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="B101" s="1" t="inlineStr">
         <is>
           <t>KLASYFIKACJA GENERALNA PUCHARU (12 RUND)</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="3" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>Poz.</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>Zawodnik</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="I102" s="3" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="K90" s="3" t="inlineStr">
+      <c r="K102" s="3" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="L90" s="3" t="inlineStr">
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="M90" s="3" t="inlineStr">
+      <c r="M102" s="3" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="N90" s="3" t="inlineStr">
+      <c r="N102" s="3" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="O90" s="3" t="inlineStr">
+      <c r="O102" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="P90" s="3" t="inlineStr">
+      <c r="P102" s="3" t="inlineStr">
         <is>
           <t>SUMA</t>
         </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" s="39" t="inlineStr">
-        <is>
-          <t>RDX</t>
-        </is>
-      </c>
-      <c r="D91" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="E91" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="F91" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="G91" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="H91" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="I91" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="J91" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="K91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P91" s="29" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>SIW</t>
-        </is>
-      </c>
-      <c r="D92" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="E92" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="F92" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="G92" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="H92" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I92" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="J92" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="K92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O92" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P92" s="29" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="C93" s="39" t="inlineStr">
-        <is>
-          <t>BĄB</t>
-        </is>
-      </c>
-      <c r="D93" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="E93" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="F93" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="G93" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="H93" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="I93" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="J93" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="K93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O93" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P93" s="29" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="D94" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="E94" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="F94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="H94" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="I94" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="J94" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="K94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O94" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P94" s="29" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C95" s="39" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="D95" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="E95" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="F95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="H95" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="I95" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="J95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O95" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P95" s="29" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C96" s="41" t="inlineStr">
-        <is>
-          <t>KRO</t>
-        </is>
-      </c>
-      <c r="D96" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="F96" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="G96" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="H96" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="I96" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="J96" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M96" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N96" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O96" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P96" s="29" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="C97" s="39" t="inlineStr">
-        <is>
-          <t>PYR</t>
-        </is>
-      </c>
-      <c r="D97" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="E97" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F97" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="G97" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="H97" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="I97" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="J97" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="K97" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P97" s="29" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>SZP</t>
-        </is>
-      </c>
-      <c r="D98" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E98" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F98" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="G98" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I98" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="J98" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K98" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L98" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M98" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N98" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O98" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P98" s="29" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="C99" s="39" t="inlineStr">
-        <is>
-          <t>PAW</t>
-        </is>
-      </c>
-      <c r="D99" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="E99" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="F99" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="H99" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I99" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="J99" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P99" s="29" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="41" t="n">
-        <v>10</v>
-      </c>
-      <c r="C100" s="41" t="inlineStr">
-        <is>
-          <t>DAR</t>
-        </is>
-      </c>
-      <c r="D100" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F100" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="G100" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="H100" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="I100" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="J100" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="K100" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L100" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M100" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N100" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O100" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P100" s="29" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="39" t="n">
-        <v>11</v>
-      </c>
-      <c r="C101" s="39" t="inlineStr">
-        <is>
-          <t>KAL</t>
-        </is>
-      </c>
-      <c r="D101" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="G101" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="I101" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="K101" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L101" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M101" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N101" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O101" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P101" s="29" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="41" t="n">
-        <v>12</v>
-      </c>
-      <c r="C102" s="41" t="inlineStr">
-        <is>
-          <t>TAS</t>
-        </is>
-      </c>
-      <c r="D102" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="H102" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="J102" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K102" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L102" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M102" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N102" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O102" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P102" s="29" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="39" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C103" s="39" t="inlineStr">
         <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="D103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="D103" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="E103" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="F103" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="G103" s="40" t="n">
+        <v>20</v>
       </c>
       <c r="H103" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="I103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="I103" s="40" t="n">
+        <v>20</v>
       </c>
       <c r="J103" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="K103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="K103" s="40" t="n">
+        <v>2</v>
       </c>
       <c r="L103" s="40" t="inlineStr">
         <is>
@@ -4583,51 +4353,43 @@
         </is>
       </c>
       <c r="P103" s="29" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="41" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C104" s="41" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>JAC</t>
         </is>
       </c>
       <c r="D104" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="E104" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="E104" s="42" t="n">
+        <v>9</v>
       </c>
       <c r="F104" s="42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G104" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G104" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="H104" s="42" t="n">
+        <v>20</v>
       </c>
       <c r="I104" s="42" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J104" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="K104" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="K104" s="42" t="n">
+        <v>20</v>
       </c>
       <c r="L104" s="42" t="inlineStr">
         <is>
@@ -4650,55 +4412,41 @@
         </is>
       </c>
       <c r="P104" s="29" t="n">
-        <v>21</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C105" s="39" t="inlineStr">
         <is>
-          <t>ROM</t>
-        </is>
-      </c>
-      <c r="D105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D105" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="E105" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="F105" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="G105" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="H105" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="I105" s="40" t="n">
+        <v>18</v>
       </c>
       <c r="J105" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="K105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="K105" s="40" t="n">
+        <v>14</v>
       </c>
       <c r="L105" s="40" t="inlineStr">
         <is>
@@ -4721,55 +4469,41 @@
         </is>
       </c>
       <c r="P105" s="29" t="n">
-        <v>18</v>
+        <v>109</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" s="41" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="D106" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="E106" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="F106" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="G106" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="H106" s="42" t="n">
         <v>16</v>
       </c>
-      <c r="C106" s="41" t="inlineStr">
-        <is>
-          <t>CYG</t>
-        </is>
-      </c>
-      <c r="D106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="F106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J106" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="K106" s="42" t="n">
+        <v>16</v>
       </c>
       <c r="L106" s="42" t="inlineStr">
         <is>
@@ -4792,55 +4526,45 @@
         </is>
       </c>
       <c r="P106" s="29" t="n">
-        <v>8</v>
+        <v>109</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="39" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C107" s="39" t="inlineStr">
         <is>
-          <t>DAH</t>
-        </is>
-      </c>
-      <c r="D107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="D107" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="E107" s="40" t="n">
+        <v>20</v>
       </c>
       <c r="F107" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="40" t="n">
+        <v>7</v>
       </c>
       <c r="H107" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="I107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="I107" s="40" t="n">
+        <v>14</v>
       </c>
       <c r="J107" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K107" s="40" t="n">
+        <v>18</v>
       </c>
       <c r="L107" s="40" t="inlineStr">
         <is>
@@ -4863,55 +4587,45 @@
         </is>
       </c>
       <c r="P107" s="29" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C108" s="41" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="D108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E108" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="C108" s="41" t="inlineStr">
-        <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="D108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="K108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G108" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="H108" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="I108" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J108" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="42" t="n">
+        <v>4</v>
       </c>
       <c r="L108" s="42" t="inlineStr">
         <is>
@@ -4934,55 +4648,41 @@
         </is>
       </c>
       <c r="P108" s="29" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="39" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C109" s="39" t="inlineStr">
         <is>
-          <t>BĄC</t>
-        </is>
-      </c>
-      <c r="D109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="D109" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E109" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F109" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G109" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="H109" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="I109" s="40" t="n">
+        <v>6</v>
       </c>
       <c r="J109" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="K109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="K109" s="40" t="n">
+        <v>5</v>
       </c>
       <c r="L109" s="40" t="inlineStr">
         <is>
@@ -5005,94 +4705,880 @@
         </is>
       </c>
       <c r="P109" s="29" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C110" s="41" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="D110" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E110" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="F110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="H110" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I110" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="J110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="L110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P110" s="29" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C111" s="39" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="D111" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F111" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="G111" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="J111" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="K111" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="L111" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P111" s="29" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C112" s="41" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D112" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E112" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F112" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="G112" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="H112" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I112" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="J112" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K112" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="L112" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M112" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O112" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P112" s="29" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="C113" s="39" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="D113" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E113" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="G113" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I113" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K113" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="L113" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P113" s="29" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="C114" s="41" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D114" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E114" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J114" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K114" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="L114" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M114" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O114" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P114" s="29" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C115" s="39" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D115" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E115" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="I115" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="K115" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="L115" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P115" s="29" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="C116" s="41" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="D116" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E116" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="H116" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J116" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M116" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O116" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P116" s="29" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C117" s="39" t="inlineStr">
+        <is>
+          <t>ROM</t>
+        </is>
+      </c>
+      <c r="D117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="K117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P117" s="29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="41" t="n">
+        <v>16</v>
+      </c>
+      <c r="C118" s="41" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="D118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="K118" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="L118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O118" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P118" s="29" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="C119" s="39" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E119" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P119" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="C120" s="41" t="inlineStr">
+        <is>
+          <t>DAH</t>
+        </is>
+      </c>
+      <c r="D120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="I120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P120" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="39" t="n">
+        <v>19</v>
+      </c>
+      <c r="C121" s="39" t="inlineStr">
+        <is>
+          <t>BĄC</t>
+        </is>
+      </c>
+      <c r="D121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="K121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P121" s="29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="41" t="n">
         <v>20</v>
       </c>
-      <c r="C110" s="41" t="inlineStr">
+      <c r="C122" s="41" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="D110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P110" s="29" t="n">
+      <c r="D122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P122" s="29" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
     <row r="123"/>
     <row r="124"/>
     <row r="125"/>
@@ -5110,6 +5596,18 @@
     <row r="137"/>
     <row r="138"/>
     <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>

--- a/Puchar_Lata_2026_Browar.xlsx
+++ b/Puchar_Lata_2026_Browar.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S151"/>
+  <dimension ref="A1:S168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4214,859 +4214,653 @@
       </c>
     </row>
     <row r="99"/>
-    <row r="100"/>
+    <row r="100">
+      <c r="B100" s="32" t="inlineStr">
+        <is>
+          <t>Runda IX • Piątek, 04.09.2026</t>
+        </is>
+      </c>
+    </row>
     <row r="101">
-      <c r="B101" s="1" t="inlineStr">
+      <c r="B101" s="33" t="inlineStr">
+        <is>
+          <t>Bieg</t>
+        </is>
+      </c>
+      <c r="C101" s="33" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="D101" s="33" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="E101" s="33" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="F101" s="33" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="G101" s="33" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="H101" s="33" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="I101" s="33" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="J101" s="33" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="K101" s="33" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="L101" s="33" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="M101" s="33" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="N101" s="33" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="O101" s="33" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="P101" s="33" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 1</t>
+        </is>
+      </c>
+      <c r="C102" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D102" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="E102" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="F102" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="G102" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H102" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="I102" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="J102" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="K102" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M102" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N102" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P102" s="35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 2</t>
+        </is>
+      </c>
+      <c r="C103" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F103" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G103" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H103" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I103" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="J103" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="K103" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="L103" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="M103" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P103" s="35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 3</t>
+        </is>
+      </c>
+      <c r="C104" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F104" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H104" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="J104" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="K104" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L104" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M104" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N104" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="O104" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P104" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 4</t>
+        </is>
+      </c>
+      <c r="C105" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="D105" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="E105" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F105" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G105" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H105" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L105" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="N105" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O105" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P105" s="35" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 5</t>
+        </is>
+      </c>
+      <c r="C106" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D106" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E106" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="F106" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="G106" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H106" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I106" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L106" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M106" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="N106" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O106" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="P106" s="35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="36" t="inlineStr">
+        <is>
+          <t>Suma punktów</t>
+        </is>
+      </c>
+      <c r="C107" s="29" t="n">
+        <v>49</v>
+      </c>
+      <c r="D107" s="29" t="n">
+        <v>47</v>
+      </c>
+      <c r="E107" s="29" t="n">
+        <v>45</v>
+      </c>
+      <c r="F107" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="G107" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="H107" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="I107" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="J107" s="29" t="n">
+        <v>29</v>
+      </c>
+      <c r="K107" s="29" t="n">
+        <v>28</v>
+      </c>
+      <c r="L107" s="29" t="n">
+        <v>27</v>
+      </c>
+      <c r="M107" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="N107" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="O107" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="P107" s="29" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="36" t="inlineStr">
+        <is>
+          <t>Średnia na bieg</t>
+        </is>
+      </c>
+      <c r="C108" s="31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D108" s="31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E108" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F108" s="31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G108" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H108" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I108" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J108" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K108" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L108" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M108" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N108" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O108" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P108" s="31" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="37" t="inlineStr">
+        <is>
+          <t>Miejsce</t>
+        </is>
+      </c>
+      <c r="C109" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G109" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H109" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I109" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J109" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="K109" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L109" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="M109" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N109" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="O109" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="P109" s="38" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="36" t="inlineStr">
+        <is>
+          <t>Punkty Turniejowe</t>
+        </is>
+      </c>
+      <c r="C110" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D110" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E110" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="F110" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G110" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H110" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I110" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J110" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K110" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L110" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M110" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N110" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O110" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P110" s="29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113">
+      <c r="B113" s="1" t="inlineStr">
         <is>
           <t>KLASYFIKACJA GENERALNA PUCHARU (12 RUND)</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" s="3" t="inlineStr">
+    <row r="114">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>Poz.</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>Zawodnik</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="G114" s="3" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H114" s="3" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I114" s="3" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J102" s="3" t="inlineStr">
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="K102" s="3" t="inlineStr">
+      <c r="K114" s="3" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="L102" s="3" t="inlineStr">
+      <c r="L114" s="3" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="M102" s="3" t="inlineStr">
+      <c r="M114" s="3" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="N102" s="3" t="inlineStr">
+      <c r="N114" s="3" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="O102" s="3" t="inlineStr">
+      <c r="O114" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="P102" s="3" t="inlineStr">
+      <c r="P114" s="3" t="inlineStr">
         <is>
           <t>SUMA</t>
         </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C103" s="39" t="inlineStr">
-        <is>
-          <t>RDX</t>
-        </is>
-      </c>
-      <c r="D103" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="E103" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="F103" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="G103" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="H103" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="I103" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="J103" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="K103" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P103" s="29" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="C104" s="41" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="D104" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="E104" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="F104" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="H104" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="I104" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="J104" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="K104" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="L104" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M104" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N104" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O104" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P104" s="29" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="C105" s="39" t="inlineStr">
-        <is>
-          <t>SIW</t>
-        </is>
-      </c>
-      <c r="D105" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="E105" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="F105" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="G105" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="H105" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="I105" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="J105" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="K105" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="L105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O105" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P105" s="29" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C106" s="41" t="inlineStr">
-        <is>
-          <t>BĄB</t>
-        </is>
-      </c>
-      <c r="D106" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="E106" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="F106" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="G106" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="H106" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="I106" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J106" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="K106" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="L106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O106" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P106" s="29" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C107" s="39" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="D107" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="E107" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="F107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G107" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="H107" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="I107" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="J107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K107" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="L107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O107" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P107" s="29" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C108" s="41" t="inlineStr">
-        <is>
-          <t>KRO</t>
-        </is>
-      </c>
-      <c r="D108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="F108" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="G108" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="H108" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="I108" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="J108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="L108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O108" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P108" s="29" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="C109" s="39" t="inlineStr">
-        <is>
-          <t>PYR</t>
-        </is>
-      </c>
-      <c r="D109" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="E109" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F109" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="G109" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="H109" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="I109" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="J109" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="K109" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="L109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O109" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P109" s="29" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="C110" s="41" t="inlineStr">
-        <is>
-          <t>PAW</t>
-        </is>
-      </c>
-      <c r="D110" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E110" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="F110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="H110" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="I110" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="J110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="L110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O110" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P110" s="29" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="C111" s="39" t="inlineStr">
-        <is>
-          <t>SZP</t>
-        </is>
-      </c>
-      <c r="D111" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E111" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="F111" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="G111" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="J111" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="K111" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="L111" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M111" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N111" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O111" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P111" s="29" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="41" t="n">
-        <v>10</v>
-      </c>
-      <c r="C112" s="41" t="inlineStr">
-        <is>
-          <t>DAR</t>
-        </is>
-      </c>
-      <c r="D112" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F112" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="G112" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="H112" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="I112" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="J112" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="K112" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="L112" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M112" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N112" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O112" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P112" s="29" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="39" t="n">
-        <v>11</v>
-      </c>
-      <c r="C113" s="39" t="inlineStr">
-        <is>
-          <t>KAL</t>
-        </is>
-      </c>
-      <c r="D113" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="G113" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="I113" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="K113" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="L113" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M113" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N113" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O113" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P113" s="29" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="41" t="n">
-        <v>12</v>
-      </c>
-      <c r="C114" s="41" t="inlineStr">
-        <is>
-          <t>DOM</t>
-        </is>
-      </c>
-      <c r="D114" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="E114" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I114" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="J114" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="K114" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="L114" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M114" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N114" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O114" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P114" s="29" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="39" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C115" s="39" t="inlineStr">
         <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="D115" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="D115" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="E115" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="F115" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="G115" s="40" t="n">
+        <v>20</v>
       </c>
       <c r="H115" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="I115" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="J115" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="K115" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L115" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="I115" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="K115" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="L115" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M115" s="40" t="inlineStr">
         <is>
           <t>-</t>
@@ -5083,56 +4877,44 @@
         </is>
       </c>
       <c r="P115" s="29" t="n">
-        <v>30</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C116" s="41" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="D116" s="42" t="n">
         <v>14</v>
       </c>
-      <c r="C116" s="41" t="inlineStr">
-        <is>
-          <t>TAS</t>
-        </is>
-      </c>
-      <c r="D116" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="F116" s="42" t="n">
+        <v>12</v>
       </c>
       <c r="G116" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="H116" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="I116" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J116" s="42" t="n">
         <v>14</v>
       </c>
-      <c r="H116" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="J116" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K116" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L116" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K116" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="L116" s="42" t="n">
+        <v>20</v>
       </c>
       <c r="M116" s="42" t="inlineStr">
         <is>
@@ -5150,61 +4932,45 @@
         </is>
       </c>
       <c r="P116" s="29" t="n">
-        <v>21</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C117" s="39" t="inlineStr">
         <is>
-          <t>ROM</t>
-        </is>
-      </c>
-      <c r="D117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D117" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="E117" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="F117" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="G117" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="H117" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="I117" s="40" t="n">
+        <v>18</v>
       </c>
       <c r="J117" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="K117" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="L117" s="40" t="n">
         <v>18</v>
       </c>
-      <c r="K117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M117" s="40" t="inlineStr">
         <is>
           <t>-</t>
@@ -5221,58 +4987,46 @@
         </is>
       </c>
       <c r="P117" s="29" t="n">
-        <v>18</v>
+        <v>127</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C118" s="41" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D118" s="42" t="n">
         <v>16</v>
       </c>
-      <c r="C118" s="41" t="inlineStr">
-        <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="D118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="42" t="n">
+        <v>9</v>
       </c>
       <c r="F118" s="42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G118" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="H118" s="42" t="n">
+        <v>20</v>
+      </c>
+      <c r="I118" s="42" t="n">
+        <v>16</v>
       </c>
       <c r="J118" s="42" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K118" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="L118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="L118" s="42" t="n">
+        <v>8</v>
       </c>
       <c r="M118" s="42" t="inlineStr">
         <is>
@@ -5290,60 +5044,48 @@
         </is>
       </c>
       <c r="P118" s="29" t="n">
-        <v>16</v>
+        <v>118</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="39" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C119" s="39" t="inlineStr">
         <is>
-          <t>CYG</t>
-        </is>
-      </c>
-      <c r="D119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="D119" s="40" t="n">
+        <v>20</v>
       </c>
       <c r="E119" s="40" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F119" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G119" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="H119" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="I119" s="40" t="n">
+        <v>14</v>
       </c>
       <c r="J119" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K119" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="L119" s="40" t="n">
+        <v>6</v>
       </c>
       <c r="M119" s="40" t="inlineStr">
         <is>
@@ -5361,60 +5103,48 @@
         </is>
       </c>
       <c r="P119" s="29" t="n">
-        <v>8</v>
+        <v>103</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C120" s="41" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="D120" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E120" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="C120" s="41" t="inlineStr">
-        <is>
-          <t>DAH</t>
-        </is>
-      </c>
-      <c r="D120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F120" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G120" s="42" t="n">
+        <v>10</v>
       </c>
       <c r="H120" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="I120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="I120" s="42" t="n">
+        <v>10</v>
       </c>
       <c r="J120" s="42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K120" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="L120" s="42" t="n">
+        <v>12</v>
       </c>
       <c r="M120" s="42" t="inlineStr">
         <is>
@@ -5432,60 +5162,44 @@
         </is>
       </c>
       <c r="P120" s="29" t="n">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="39" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C121" s="39" t="inlineStr">
         <is>
-          <t>BĄC</t>
-        </is>
-      </c>
-      <c r="D121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="D121" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E121" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F121" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G121" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="H121" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="I121" s="40" t="n">
+        <v>6</v>
       </c>
       <c r="J121" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="K121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="K121" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="L121" s="40" t="n">
+        <v>14</v>
       </c>
       <c r="M121" s="40" t="inlineStr">
         <is>
@@ -5503,95 +5217,939 @@
         </is>
       </c>
       <c r="P121" s="29" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C122" s="41" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="D122" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E122" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F122" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="G122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="J122" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K122" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="L122" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="M122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O122" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P122" s="29" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C123" s="39" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="D123" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E123" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F123" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="H123" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I123" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="J123" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="L123" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="M123" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P123" s="29" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C124" s="41" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D124" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E124" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F124" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="G124" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="H124" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I124" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="J124" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K124" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="L124" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="M124" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O124" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P124" s="29" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="C125" s="39" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D125" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E125" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="I125" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="K125" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="L125" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="M125" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P125" s="29" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="C126" s="41" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="D126" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E126" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="G126" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="I126" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="K126" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L126" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M126" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O126" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P126" s="29" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C127" s="39" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D127" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E127" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="J127" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K127" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="L127" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P127" s="29" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="C128" s="41" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="D128" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E128" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="H128" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J128" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K128" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M128" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O128" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P128" s="29" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C129" s="39" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="D129" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E129" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="K129" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="L129" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M129" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P129" s="29" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="41" t="n">
+        <v>16</v>
+      </c>
+      <c r="C130" s="41" t="inlineStr">
+        <is>
+          <t>ROM</t>
+        </is>
+      </c>
+      <c r="D130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J130" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="K130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O130" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P130" s="29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="C131" s="39" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E131" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P131" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="C132" s="41" t="inlineStr">
+        <is>
+          <t>DAH</t>
+        </is>
+      </c>
+      <c r="D132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="I132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P132" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="39" t="n">
+        <v>19</v>
+      </c>
+      <c r="C133" s="39" t="inlineStr">
+        <is>
+          <t>BĄC</t>
+        </is>
+      </c>
+      <c r="D133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="K133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P133" s="29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="41" t="n">
         <v>20</v>
       </c>
-      <c r="C122" s="41" t="inlineStr">
+      <c r="C134" s="41" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="D134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="M134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O134" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P134" s="29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="39" t="n">
+        <v>21</v>
+      </c>
+      <c r="C135" s="39" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="D122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P122" s="29" t="n">
+      <c r="D135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P135" s="29" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
     <row r="136"/>
     <row r="137"/>
     <row r="138"/>
@@ -5608,6 +6166,23 @@
     <row r="149"/>
     <row r="150"/>
     <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>

--- a/Puchar_Lata_2026_Browar.xlsx
+++ b/Puchar_Lata_2026_Browar.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S168"/>
+  <dimension ref="A1:S180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4740,841 +4740,559 @@
       </c>
     </row>
     <row r="111"/>
-    <row r="112"/>
+    <row r="112">
+      <c r="B112" s="32" t="inlineStr">
+        <is>
+          <t>Runda X • Piątek, 11.09.2026</t>
+        </is>
+      </c>
+    </row>
     <row r="113">
-      <c r="B113" s="1" t="inlineStr">
+      <c r="B113" s="33" t="inlineStr">
+        <is>
+          <t>Bieg</t>
+        </is>
+      </c>
+      <c r="C113" s="33" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D113" s="33" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="E113" s="33" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="F113" s="33" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="G113" s="33" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="H113" s="33" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="I113" s="33" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="J113" s="33" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="K113" s="33" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="L113" s="33" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="M113" s="33" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 1</t>
+        </is>
+      </c>
+      <c r="C114" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D114" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="E114" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F114" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="G114" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="I114" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J114" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K114" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 2</t>
+        </is>
+      </c>
+      <c r="C115" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D115" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="G115" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H115" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="I115" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L115" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M115" s="35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 3</t>
+        </is>
+      </c>
+      <c r="C116" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D116" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E116" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="F116" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G116" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="H116" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J116" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K116" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L116" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 4</t>
+        </is>
+      </c>
+      <c r="C117" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D117" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E117" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F117" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="H117" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I117" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J117" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K117" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="L117" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M117" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 5</t>
+        </is>
+      </c>
+      <c r="C118" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="D118" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E118" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="F118" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G118" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H118" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J118" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L118" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M118" s="35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="36" t="inlineStr">
+        <is>
+          <t>Suma punktów</t>
+        </is>
+      </c>
+      <c r="C119" s="29" t="n">
+        <v>39</v>
+      </c>
+      <c r="D119" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="E119" s="29" t="n">
+        <v>32</v>
+      </c>
+      <c r="F119" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="G119" s="29" t="n">
+        <v>29</v>
+      </c>
+      <c r="H119" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="I119" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="J119" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="K119" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="L119" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="M119" s="29" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="36" t="inlineStr">
+        <is>
+          <t>Średnia na bieg</t>
+        </is>
+      </c>
+      <c r="C120" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D120" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E120" s="31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F120" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G120" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H120" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I120" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J120" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K120" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L120" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M120" s="31" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="37" t="inlineStr">
+        <is>
+          <t>Miejsce</t>
+        </is>
+      </c>
+      <c r="C121" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G121" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H121" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I121" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J121" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="K121" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L121" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="M121" s="38" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="36" t="inlineStr">
+        <is>
+          <t>Punkty Turniejowe</t>
+        </is>
+      </c>
+      <c r="C122" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D122" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E122" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="F122" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G122" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H122" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I122" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J122" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K122" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L122" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M122" s="29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125">
+      <c r="B125" s="1" t="inlineStr">
         <is>
           <t>KLASYFIKACJA GENERALNA PUCHARU (12 RUND)</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="B114" s="3" t="inlineStr">
+    <row r="126">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>Poz.</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>Zawodnik</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H126" s="3" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="I114" s="3" t="inlineStr">
+      <c r="I126" s="3" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J114" s="3" t="inlineStr">
+      <c r="J126" s="3" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="K114" s="3" t="inlineStr">
+      <c r="K126" s="3" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="L114" s="3" t="inlineStr">
+      <c r="L126" s="3" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="M114" s="3" t="inlineStr">
+      <c r="M126" s="3" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="N114" s="3" t="inlineStr">
+      <c r="N126" s="3" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="O114" s="3" t="inlineStr">
+      <c r="O126" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="P114" s="3" t="inlineStr">
+      <c r="P126" s="3" t="inlineStr">
         <is>
           <t>SUMA</t>
         </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C115" s="39" t="inlineStr">
-        <is>
-          <t>RDX</t>
-        </is>
-      </c>
-      <c r="D115" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="E115" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="F115" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="G115" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="H115" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="I115" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="J115" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="K115" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L115" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="M115" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N115" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O115" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P115" s="29" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="C116" s="41" t="inlineStr">
-        <is>
-          <t>BĄB</t>
-        </is>
-      </c>
-      <c r="D116" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="E116" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="F116" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="G116" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="H116" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="I116" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J116" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="K116" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="L116" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="M116" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N116" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O116" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P116" s="29" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="C117" s="39" t="inlineStr">
-        <is>
-          <t>SIW</t>
-        </is>
-      </c>
-      <c r="D117" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="E117" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="F117" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="G117" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="H117" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="I117" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="J117" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="K117" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="L117" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="M117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O117" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P117" s="29" t="n">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C118" s="41" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="D118" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="E118" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="F118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="H118" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="I118" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="J118" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="K118" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="L118" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="M118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O118" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P118" s="29" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C119" s="39" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="D119" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="E119" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="F119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="H119" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="I119" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="J119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K119" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="L119" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="M119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O119" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P119" s="29" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C120" s="41" t="inlineStr">
-        <is>
-          <t>KRO</t>
-        </is>
-      </c>
-      <c r="D120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="F120" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="G120" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="H120" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="I120" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="J120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="L120" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="M120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O120" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P120" s="29" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="C121" s="39" t="inlineStr">
-        <is>
-          <t>PYR</t>
-        </is>
-      </c>
-      <c r="D121" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="E121" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F121" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="G121" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="H121" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="I121" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="J121" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="K121" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="L121" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="M121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O121" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P121" s="29" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="C122" s="41" t="inlineStr">
-        <is>
-          <t>SZP</t>
-        </is>
-      </c>
-      <c r="D122" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E122" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F122" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="G122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I122" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="J122" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K122" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="L122" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="M122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O122" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P122" s="29" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="C123" s="39" t="inlineStr">
-        <is>
-          <t>PAW</t>
-        </is>
-      </c>
-      <c r="D123" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="E123" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="F123" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="H123" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I123" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="J123" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="L123" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="M123" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N123" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O123" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P123" s="29" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="41" t="n">
-        <v>10</v>
-      </c>
-      <c r="C124" s="41" t="inlineStr">
-        <is>
-          <t>DAR</t>
-        </is>
-      </c>
-      <c r="D124" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F124" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="G124" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="H124" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="I124" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="J124" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="K124" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="L124" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="M124" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N124" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O124" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P124" s="29" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="39" t="n">
-        <v>11</v>
-      </c>
-      <c r="C125" s="39" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="D125" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="I125" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="K125" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="L125" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="M125" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N125" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O125" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P125" s="29" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="41" t="n">
-        <v>12</v>
-      </c>
-      <c r="C126" s="41" t="inlineStr">
-        <is>
-          <t>KAL</t>
-        </is>
-      </c>
-      <c r="D126" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="G126" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="I126" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J126" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="K126" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L126" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M126" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N126" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O126" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P126" s="29" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="39" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C127" s="39" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>RDX</t>
         </is>
       </c>
       <c r="D127" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="E127" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F127" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="E127" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="F127" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="G127" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="H127" s="40" t="n">
+        <v>10</v>
       </c>
       <c r="I127" s="40" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J127" s="40" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K127" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="L127" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="L127" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="M127" s="40" t="n">
+        <v>18</v>
       </c>
       <c r="N127" s="40" t="inlineStr">
         <is>
@@ -5587,59 +5305,47 @@
         </is>
       </c>
       <c r="P127" s="29" t="n">
-        <v>31</v>
+        <v>147</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C128" s="41" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D128" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="E128" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="F128" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="G128" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="H128" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I128" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="J128" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="K128" s="42" t="n">
         <v>14</v>
       </c>
-      <c r="C128" s="41" t="inlineStr">
-        <is>
-          <t>TAS</t>
-        </is>
-      </c>
-      <c r="D128" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="H128" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="J128" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="K128" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L128" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="M128" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="M128" s="42" t="n">
+        <v>20</v>
       </c>
       <c r="N128" s="42" t="inlineStr">
         <is>
@@ -5652,61 +5358,47 @@
         </is>
       </c>
       <c r="P128" s="29" t="n">
-        <v>23</v>
+        <v>147</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" s="39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C129" s="39" t="inlineStr">
         <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="D129" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="D129" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="E129" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F129" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="G129" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="H129" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="I129" s="40" t="n">
+        <v>7</v>
       </c>
       <c r="J129" s="40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K129" s="40" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L129" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="M129" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="M129" s="40" t="n">
+        <v>5</v>
       </c>
       <c r="N129" s="40" t="inlineStr">
         <is>
@@ -5719,65 +5411,49 @@
         </is>
       </c>
       <c r="P129" s="29" t="n">
-        <v>19</v>
+        <v>134</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C130" s="41" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D130" s="42" t="n">
         <v>16</v>
       </c>
-      <c r="C130" s="41" t="inlineStr">
-        <is>
-          <t>ROM</t>
-        </is>
-      </c>
-      <c r="D130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E130" s="42" t="n">
+        <v>9</v>
       </c>
       <c r="F130" s="42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="H130" s="42" t="n">
+        <v>20</v>
+      </c>
+      <c r="I130" s="42" t="n">
+        <v>16</v>
       </c>
       <c r="J130" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="K130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="K130" s="42" t="n">
+        <v>20</v>
+      </c>
+      <c r="L130" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="M130" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="N130" s="42" t="inlineStr">
         <is>
@@ -5790,65 +5466,51 @@
         </is>
       </c>
       <c r="P130" s="29" t="n">
-        <v>18</v>
+        <v>124</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" s="39" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C131" s="39" t="inlineStr">
         <is>
-          <t>CYG</t>
-        </is>
-      </c>
-      <c r="D131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="D131" s="40" t="n">
+        <v>20</v>
       </c>
       <c r="E131" s="40" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F131" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="H131" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="I131" s="40" t="n">
+        <v>14</v>
       </c>
       <c r="J131" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K131" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="L131" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="M131" s="40" t="n">
+        <v>16</v>
       </c>
       <c r="N131" s="40" t="inlineStr">
         <is>
@@ -5861,65 +5523,51 @@
         </is>
       </c>
       <c r="P131" s="29" t="n">
-        <v>8</v>
+        <v>119</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C132" s="41" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="D132" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E132" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="C132" s="41" t="inlineStr">
-        <is>
-          <t>DAH</t>
-        </is>
-      </c>
-      <c r="D132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F132" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G132" s="42" t="n">
+        <v>10</v>
       </c>
       <c r="H132" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="I132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="I132" s="42" t="n">
+        <v>10</v>
       </c>
       <c r="J132" s="42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K132" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="L132" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="M132" s="42" t="n">
+        <v>14</v>
       </c>
       <c r="N132" s="42" t="inlineStr">
         <is>
@@ -5932,65 +5580,47 @@
         </is>
       </c>
       <c r="P132" s="29" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" s="39" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C133" s="39" t="inlineStr">
         <is>
-          <t>BĄC</t>
-        </is>
-      </c>
-      <c r="D133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="D133" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E133" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F133" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G133" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="H133" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="I133" s="40" t="n">
+        <v>6</v>
       </c>
       <c r="J133" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="K133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="K133" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="L133" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="M133" s="40" t="n">
+        <v>10</v>
       </c>
       <c r="N133" s="40" t="inlineStr">
         <is>
@@ -6003,32 +5633,26 @@
         </is>
       </c>
       <c r="P133" s="29" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" s="41" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C134" s="41" t="inlineStr">
         <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="D134" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E134" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F134" s="42" t="n">
+        <v>14</v>
       </c>
       <c r="G134" s="42" t="inlineStr">
         <is>
@@ -6040,28 +5664,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="J134" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K134" s="42" t="n">
+        <v>6</v>
       </c>
       <c r="L134" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="M134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="M134" s="42" t="n">
+        <v>7</v>
       </c>
       <c r="N134" s="42" t="inlineStr">
         <is>
@@ -6074,94 +5690,874 @@
         </is>
       </c>
       <c r="P134" s="29" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C135" s="39" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="D135" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E135" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="H135" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I135" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="J135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="L135" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="M135" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="N135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P135" s="29" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C136" s="41" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D136" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E136" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F136" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="G136" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="H136" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I136" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="J136" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K136" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="M136" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O136" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P136" s="29" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="C137" s="39" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D137" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="E137" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="J137" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K137" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="L137" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="N137" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P137" s="29" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="C138" s="41" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D138" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E138" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H138" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="I138" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="K138" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="L138" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M138" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O138" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P138" s="29" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C139" s="39" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="D139" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E139" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="G139" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I139" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K139" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="L139" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P139" s="29" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="C140" s="41" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="D140" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E140" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="H140" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J140" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K140" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M140" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="N140" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O140" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P140" s="29" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C141" s="39" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="D141" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E141" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="K141" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="L141" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M141" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O141" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P141" s="29" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="41" t="n">
+        <v>16</v>
+      </c>
+      <c r="C142" s="41" t="inlineStr">
+        <is>
+          <t>ROM</t>
+        </is>
+      </c>
+      <c r="D142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="K142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P142" s="29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="C143" s="39" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E143" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P143" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="C144" s="41" t="inlineStr">
+        <is>
+          <t>DAH</t>
+        </is>
+      </c>
+      <c r="D144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="I144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P144" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="39" t="n">
+        <v>19</v>
+      </c>
+      <c r="C145" s="39" t="inlineStr">
+        <is>
+          <t>BĄC</t>
+        </is>
+      </c>
+      <c r="D145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="K145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P145" s="29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C146" s="41" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="D146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L146" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="M146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O146" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P146" s="29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="C135" s="39" t="inlineStr">
+      <c r="C147" s="39" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="D135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P135" s="29" t="n">
+      <c r="D147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P147" s="29" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
     <row r="148"/>
     <row r="149"/>
     <row r="150"/>
@@ -6183,6 +6579,18 @@
     <row r="166"/>
     <row r="167"/>
     <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>

--- a/Puchar_Lata_2026_Browar.xlsx
+++ b/Puchar_Lata_2026_Browar.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S180"/>
+  <dimension ref="A1:S197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5170,826 +5170,658 @@
       </c>
     </row>
     <row r="123"/>
-    <row r="124"/>
+    <row r="124">
+      <c r="B124" s="32" t="inlineStr">
+        <is>
+          <t>Runda XI • Piątek, 18.09.2026</t>
+        </is>
+      </c>
+    </row>
     <row r="125">
-      <c r="B125" s="1" t="inlineStr">
+      <c r="B125" s="33" t="inlineStr">
+        <is>
+          <t>Bieg</t>
+        </is>
+      </c>
+      <c r="C125" s="33" t="inlineStr">
+        <is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D125" s="33" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="E125" s="33" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="F125" s="33" t="inlineStr">
+        <is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="G125" s="33" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="H125" s="33" t="inlineStr">
+        <is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="I125" s="33" t="inlineStr">
+        <is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="J125" s="33" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="K125" s="33" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="L125" s="33" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="M125" s="33" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="N125" s="33" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="O125" s="33" t="inlineStr">
+        <is>
+          <t>TOM</t>
+        </is>
+      </c>
+      <c r="P125" s="33" t="inlineStr">
+        <is>
+          <t>PYR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 1</t>
+        </is>
+      </c>
+      <c r="C126" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D126" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E126" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="F126" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="G126" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H126" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="I126" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="J126" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K126" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L126" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M126" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="N126" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" s="35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 2</t>
+        </is>
+      </c>
+      <c r="C127" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D127" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="E127" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="F127" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G127" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H127" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I127" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="J127" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L127" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="O127" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P127" s="35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 3</t>
+        </is>
+      </c>
+      <c r="C128" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D128" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="F128" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="G128" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H128" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I128" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K128" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L128" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="M128" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="N128" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="P128" s="35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 4</t>
+        </is>
+      </c>
+      <c r="C129" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D129" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="E129" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F129" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="G129" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H129" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I129" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J129" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K129" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="L129" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="M129" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N129" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P129" s="35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="34" t="inlineStr">
+        <is>
+          <t>Bieg 5</t>
+        </is>
+      </c>
+      <c r="C130" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D130" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="E130" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="G130" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="H130" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I130" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="J130" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="K130" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L130" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M130" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N130" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="O130" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" s="35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="36" t="inlineStr">
+        <is>
+          <t>Suma punktów</t>
+        </is>
+      </c>
+      <c r="C131" s="29" t="n">
+        <v>58</v>
+      </c>
+      <c r="D131" s="29" t="n">
+        <v>50</v>
+      </c>
+      <c r="E131" s="29" t="n">
+        <v>43</v>
+      </c>
+      <c r="F131" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="G131" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="H131" s="29" t="n">
+        <v>36</v>
+      </c>
+      <c r="I131" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="J131" s="29" t="n">
+        <v>28</v>
+      </c>
+      <c r="K131" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="L131" s="29" t="n">
+        <v>24</v>
+      </c>
+      <c r="M131" s="29" t="n">
+        <v>22</v>
+      </c>
+      <c r="N131" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="O131" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="P131" s="29" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="36" t="inlineStr">
+        <is>
+          <t>Średnia na bieg</t>
+        </is>
+      </c>
+      <c r="C132" s="31" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D132" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E132" s="31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F132" s="31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G132" s="31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H132" s="31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I132" s="31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J132" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K132" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="L132" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M132" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N132" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="O132" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P132" s="31" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="37" t="inlineStr">
+        <is>
+          <t>Miejsce</t>
+        </is>
+      </c>
+      <c r="C133" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="G133" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H133" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I133" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="J133" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="K133" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L133" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="M133" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N133" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="O133" s="38" t="n">
+        <v>13</v>
+      </c>
+      <c r="P133" s="38" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="36" t="inlineStr">
+        <is>
+          <t>Punkty Turniejowe</t>
+        </is>
+      </c>
+      <c r="C134" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D134" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="E134" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="F134" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="G134" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H134" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I134" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="J134" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K134" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L134" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M134" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N134" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O134" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P134" s="29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137">
+      <c r="B137" s="1" t="inlineStr">
         <is>
           <t>KLASYFIKACJA GENERALNA PUCHARU (12 RUND)</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="B126" s="3" t="inlineStr">
+    <row r="138">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>Poz.</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>Zawodnik</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="G126" s="3" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="I126" s="3" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="J126" s="3" t="inlineStr">
+      <c r="J138" s="3" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="K126" s="3" t="inlineStr">
+      <c r="K138" s="3" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="L126" s="3" t="inlineStr">
+      <c r="L138" s="3" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="M126" s="3" t="inlineStr">
+      <c r="M138" s="3" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="N126" s="3" t="inlineStr">
+      <c r="N138" s="3" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="O126" s="3" t="inlineStr">
+      <c r="O138" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="P126" s="3" t="inlineStr">
+      <c r="P138" s="3" t="inlineStr">
         <is>
           <t>SUMA</t>
         </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C127" s="39" t="inlineStr">
-        <is>
-          <t>RDX</t>
-        </is>
-      </c>
-      <c r="D127" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="E127" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="F127" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="G127" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="H127" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="I127" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="J127" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="K127" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L127" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="M127" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="N127" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P127" s="29" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="C128" s="41" t="inlineStr">
-        <is>
-          <t>SIW</t>
-        </is>
-      </c>
-      <c r="D128" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="E128" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="F128" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="G128" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="H128" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I128" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="J128" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="K128" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="L128" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="M128" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="N128" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O128" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P128" s="29" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="C129" s="39" t="inlineStr">
-        <is>
-          <t>BĄB</t>
-        </is>
-      </c>
-      <c r="D129" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="E129" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="F129" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="G129" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="H129" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="I129" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="J129" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="K129" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="L129" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="M129" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="N129" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O129" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P129" s="29" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C130" s="41" t="inlineStr">
-        <is>
-          <t>JAC</t>
-        </is>
-      </c>
-      <c r="D130" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="E130" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="F130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="H130" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="I130" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="J130" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="K130" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="L130" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="M130" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="N130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O130" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P130" s="29" t="n">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="C131" s="39" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="D131" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="E131" s="40" t="n">
-        <v>20</v>
-      </c>
-      <c r="F131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="H131" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="I131" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="J131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K131" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="L131" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="M131" s="40" t="n">
-        <v>16</v>
-      </c>
-      <c r="N131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O131" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P131" s="29" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C132" s="41" t="inlineStr">
-        <is>
-          <t>KRO</t>
-        </is>
-      </c>
-      <c r="D132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="42" t="n">
-        <v>18</v>
-      </c>
-      <c r="F132" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="G132" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="H132" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="I132" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="J132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="L132" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="M132" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="N132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O132" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P132" s="29" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="C133" s="39" t="inlineStr">
-        <is>
-          <t>PYR</t>
-        </is>
-      </c>
-      <c r="D133" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="E133" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="F133" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="G133" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="H133" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="I133" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="J133" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="K133" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="L133" s="40" t="n">
-        <v>14</v>
-      </c>
-      <c r="M133" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="N133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O133" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P133" s="29" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="C134" s="41" t="inlineStr">
-        <is>
-          <t>SZP</t>
-        </is>
-      </c>
-      <c r="D134" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E134" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F134" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="G134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I134" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="J134" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K134" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="L134" s="42" t="n">
-        <v>16</v>
-      </c>
-      <c r="M134" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O134" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P134" s="29" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="C135" s="39" t="inlineStr">
-        <is>
-          <t>PAW</t>
-        </is>
-      </c>
-      <c r="D135" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="E135" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="F135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="H135" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I135" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="J135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="L135" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="M135" s="40" t="n">
-        <v>9</v>
-      </c>
-      <c r="N135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O135" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P135" s="29" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="B136" s="41" t="n">
-        <v>10</v>
-      </c>
-      <c r="C136" s="41" t="inlineStr">
-        <is>
-          <t>DAR</t>
-        </is>
-      </c>
-      <c r="D136" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E136" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F136" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="G136" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="H136" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="I136" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="J136" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="K136" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="L136" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="M136" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N136" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O136" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P136" s="29" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="39" t="n">
-        <v>11</v>
-      </c>
-      <c r="C137" s="39" t="inlineStr">
-        <is>
-          <t>DOM</t>
-        </is>
-      </c>
-      <c r="D137" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="E137" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F137" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G137" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I137" s="40" t="n">
-        <v>8</v>
-      </c>
-      <c r="J137" s="40" t="n">
-        <v>5</v>
-      </c>
-      <c r="K137" s="40" t="n">
-        <v>10</v>
-      </c>
-      <c r="L137" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M137" s="40" t="n">
-        <v>12</v>
-      </c>
-      <c r="N137" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O137" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P137" s="29" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" s="41" t="n">
-        <v>12</v>
-      </c>
-      <c r="C138" s="41" t="inlineStr">
-        <is>
-          <t>HAL</t>
-        </is>
-      </c>
-      <c r="D138" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E138" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G138" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="I138" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J138" s="42" t="n">
-        <v>12</v>
-      </c>
-      <c r="K138" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="L138" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M138" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N138" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O138" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P138" s="29" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="39" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C139" s="39" t="inlineStr">
         <is>
-          <t>KAL</t>
-        </is>
-      </c>
-      <c r="D139" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E139" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SIW</t>
+        </is>
+      </c>
+      <c r="D139" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="E139" s="40" t="n">
+        <v>16</v>
       </c>
       <c r="F139" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="G139" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="H139" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="I139" s="40" t="n">
         <v>18</v>
       </c>
-      <c r="G139" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H139" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="I139" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J139" s="40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K139" s="40" t="n">
-        <v>7</v>
-      </c>
-      <c r="L139" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M139" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N139" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="L139" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="M139" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="N139" s="40" t="n">
+        <v>20</v>
       </c>
       <c r="O139" s="40" t="inlineStr">
         <is>
@@ -5997,62 +5829,50 @@
         </is>
       </c>
       <c r="P139" s="29" t="n">
-        <v>33</v>
+        <v>167</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C140" s="41" t="inlineStr">
+        <is>
+          <t>RDX</t>
+        </is>
+      </c>
+      <c r="D140" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="E140" s="42" t="n">
         <v>14</v>
       </c>
-      <c r="C140" s="41" t="inlineStr">
-        <is>
-          <t>TAS</t>
-        </is>
-      </c>
-      <c r="D140" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E140" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F140" s="42" t="n">
+        <v>20</v>
       </c>
       <c r="G140" s="42" t="n">
-        <v>14</v>
-      </c>
-      <c r="H140" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H140" s="42" t="n">
+        <v>10</v>
       </c>
       <c r="I140" s="42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J140" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="K140" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="K140" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L140" s="42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M140" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="N140" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="N140" s="42" t="n">
+        <v>16</v>
       </c>
       <c r="O140" s="42" t="inlineStr">
         <is>
@@ -6060,66 +5880,50 @@
         </is>
       </c>
       <c r="P140" s="29" t="n">
-        <v>31</v>
+        <v>163</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C141" s="39" t="inlineStr">
         <is>
-          <t>BAR</t>
-        </is>
-      </c>
-      <c r="D141" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E141" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F141" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G141" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H141" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I141" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BĄB</t>
+        </is>
+      </c>
+      <c r="D141" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="E141" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F141" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="G141" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="H141" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="I141" s="40" t="n">
+        <v>7</v>
       </c>
       <c r="J141" s="40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K141" s="40" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L141" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="M141" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N141" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="M141" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="N141" s="40" t="n">
+        <v>10</v>
       </c>
       <c r="O141" s="40" t="inlineStr">
         <is>
@@ -6127,141 +5931,107 @@
         </is>
       </c>
       <c r="P141" s="29" t="n">
-        <v>19</v>
+        <v>144</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C142" s="41" t="inlineStr">
+        <is>
+          <t>DAN</t>
+        </is>
+      </c>
+      <c r="D142" s="42" t="n">
+        <v>20</v>
+      </c>
+      <c r="E142" s="42" t="n">
+        <v>20</v>
+      </c>
+      <c r="F142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H142" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="I142" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="J142" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="L142" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="M142" s="42" t="n">
         <v>16</v>
       </c>
-      <c r="C142" s="41" t="inlineStr">
-        <is>
-          <t>ROM</t>
-        </is>
-      </c>
-      <c r="D142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J142" s="42" t="n">
+      <c r="N142" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="K142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N142" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="O142" s="42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="P142" s="29" t="n">
-        <v>18</v>
+        <v>137</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" s="39" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C143" s="39" t="inlineStr">
         <is>
-          <t>CYG</t>
-        </is>
-      </c>
-      <c r="D143" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>JAC</t>
+        </is>
+      </c>
+      <c r="D143" s="40" t="n">
+        <v>16</v>
       </c>
       <c r="E143" s="40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F143" s="40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G143" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H143" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I143" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J143" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K143" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L143" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M143" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N143" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G143" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="H143" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="I143" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="J143" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="K143" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="L143" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="M143" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="N143" s="40" t="n">
+        <v>9</v>
       </c>
       <c r="O143" s="40" t="inlineStr">
         <is>
@@ -6269,70 +6039,54 @@
         </is>
       </c>
       <c r="P143" s="29" t="n">
-        <v>8</v>
+        <v>133</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C144" s="41" t="inlineStr">
+        <is>
+          <t>KRO</t>
+        </is>
+      </c>
+      <c r="D144" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E144" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="C144" s="41" t="inlineStr">
-        <is>
-          <t>DAH</t>
-        </is>
-      </c>
-      <c r="D144" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E144" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F144" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G144" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F144" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G144" s="42" t="n">
+        <v>10</v>
       </c>
       <c r="H144" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="I144" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="I144" s="42" t="n">
+        <v>10</v>
       </c>
       <c r="J144" s="42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K144" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L144" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M144" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N144" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K144" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="L144" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="M144" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="N144" s="42" t="n">
+        <v>12</v>
       </c>
       <c r="O144" s="42" t="inlineStr">
         <is>
@@ -6340,32 +6094,26 @@
         </is>
       </c>
       <c r="P144" s="29" t="n">
-        <v>8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" s="39" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C145" s="39" t="inlineStr">
         <is>
-          <t>BĄC</t>
-        </is>
-      </c>
-      <c r="D145" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E145" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F145" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SZP</t>
+        </is>
+      </c>
+      <c r="D145" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E145" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" s="40" t="n">
+        <v>14</v>
       </c>
       <c r="G145" s="40" t="inlineStr">
         <is>
@@ -6377,33 +6125,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I145" s="40" t="n">
+        <v>12</v>
       </c>
       <c r="J145" s="40" t="n">
-        <v>6</v>
-      </c>
-      <c r="K145" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L145" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M145" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N145" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="K145" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="L145" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="M145" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="N145" s="40" t="n">
+        <v>14</v>
       </c>
       <c r="O145" s="40" t="inlineStr">
         <is>
@@ -6411,70 +6149,50 @@
         </is>
       </c>
       <c r="P145" s="29" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="41" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C146" s="41" t="inlineStr">
         <is>
-          <t>AND</t>
-        </is>
-      </c>
-      <c r="D146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PYR</t>
+        </is>
+      </c>
+      <c r="D146" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="E146" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F146" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="G146" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H146" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="I146" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="J146" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="K146" s="42" t="n">
+        <v>5</v>
       </c>
       <c r="L146" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="M146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N146" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="M146" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="N146" s="42" t="n">
+        <v>2</v>
       </c>
       <c r="O146" s="42" t="inlineStr">
         <is>
@@ -6482,95 +6200,935 @@
         </is>
       </c>
       <c r="P146" s="29" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C147" s="39" t="inlineStr">
+        <is>
+          <t>PAW</t>
+        </is>
+      </c>
+      <c r="D147" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E147" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="H147" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I147" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="J147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="L147" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="M147" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="N147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P147" s="29" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C148" s="41" t="inlineStr">
+        <is>
+          <t>DOM</t>
+        </is>
+      </c>
+      <c r="D148" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="E148" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J148" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K148" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="L148" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M148" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="N148" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="O148" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P148" s="29" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="C149" s="39" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+      <c r="D149" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E149" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F149" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G149" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="H149" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I149" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="J149" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L149" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="M149" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O149" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P149" s="29" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="C150" s="41" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D150" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E150" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="I150" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="K150" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="L150" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M150" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O150" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P150" s="29" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C151" s="39" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="D151" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="G151" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I151" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K151" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="L151" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M151" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="O151" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P151" s="29" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="C152" s="41" t="inlineStr">
+        <is>
+          <t>TAS</t>
+        </is>
+      </c>
+      <c r="D152" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E152" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F152" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="H152" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J152" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K152" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L152" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M152" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="N152" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="O152" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P152" s="29" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C153" s="39" t="inlineStr">
+        <is>
+          <t>BAR</t>
+        </is>
+      </c>
+      <c r="D153" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E153" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="K153" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="L153" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="M153" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="O153" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P153" s="29" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="41" t="n">
+        <v>16</v>
+      </c>
+      <c r="C154" s="41" t="inlineStr">
+        <is>
+          <t>ROM</t>
+        </is>
+      </c>
+      <c r="D154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" s="42" t="n">
+        <v>18</v>
+      </c>
+      <c r="K154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O154" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P154" s="29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="39" t="n">
+        <v>17</v>
+      </c>
+      <c r="C155" s="39" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E155" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P155" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="C156" s="41" t="inlineStr">
+        <is>
+          <t>DAH</t>
+        </is>
+      </c>
+      <c r="D156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="I156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O156" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P156" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="39" t="n">
+        <v>19</v>
+      </c>
+      <c r="C157" s="39" t="inlineStr">
+        <is>
+          <t>BĄC</t>
+        </is>
+      </c>
+      <c r="D157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="K157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P157" s="29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C158" s="41" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
+      <c r="D158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L158" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="M158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O158" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P158" s="29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="C147" s="39" t="inlineStr">
+      <c r="C159" s="39" t="inlineStr">
+        <is>
+          <t>TOM</t>
+        </is>
+      </c>
+      <c r="D159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O159" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P159" s="29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="41" t="n">
+        <v>22</v>
+      </c>
+      <c r="C160" s="41" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="D147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O147" s="40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P147" s="29" t="n">
+      <c r="D160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O160" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P160" s="29" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
     <row r="161"/>
     <row r="162"/>
     <row r="163"/>
@@ -6591,6 +7149,23 @@
     <row r="178"/>
     <row r="179"/>
     <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
